--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:29</t>
+    <t xml:space="preserve">2026-09-10 01:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:45</t>
+    <t xml:space="preserve">2026-09-12 22:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:56</t>
+    <t xml:space="preserve">2026-09-23 15:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2018_los_rios.xlsx
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:47</t>
+    <t xml:space="preserve">2026-10-05 17:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
